--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2065-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2065-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{139736A7-4675-4B9D-B481-B59D00B9A76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEC788B5-4320-4216-A3D9-A709BA49399A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4D49C72C-C0AC-42A3-9D30-C0871F062A52}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2F85009C-84D2-4A32-AB3F-51F4703DA5CD}"/>
   </bookViews>
   <sheets>
     <sheet name="2065-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1529,21 +1529,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE58DB3-8B1A-4212-851C-D44DADBEF302}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002D99A8-CF4D-4412-A665-95579C9A4B70}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1571,7 +1571,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1601,7 +1601,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1697,7 +1697,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2023</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2021</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2020</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>25</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2019</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2018</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2017</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2016</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2015</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2014</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2013</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2012</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
         <v>62</v>
       </c>
